--- a/results/Int Task Remove ACC 0.4/Linea_fi_explain.xlsx
+++ b/results/Int Task Remove ACC 0.4/Linea_fi_explain.xlsx
@@ -1157,7 +1157,7 @@
         <v>0.01697404716473542</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01561154160035888</v>
+        <v>0.01560304697994022</v>
       </c>
       <c r="F3" t="n">
         <v>0.002386771279338363</v>
@@ -1166,10 +1166,10 @@
         <v>0.06726859715551606</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01416526273826067</v>
+        <v>0.014160959812271</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0007394987975386436</v>
+        <v>0.0007524824274913822</v>
       </c>
       <c r="J3" t="n">
         <v>0.002320891434772618</v>
@@ -1184,10 +1184,10 @@
         <v>0.00324243873448644</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04885877760745506</v>
+        <v>0.04885448207480901</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.002546944108185829</v>
+        <v>-0.00253797482661986</v>
       </c>
       <c r="P3" t="n">
         <v>0.009899125581877392</v>
@@ -1196,7 +1196,7 @@
         <v>0.003997786427062573</v>
       </c>
       <c r="R3" t="n">
-        <v>0.007298441874193996</v>
+        <v>0.007303141122314297</v>
       </c>
       <c r="S3" t="n">
         <v>0.3338203081293302</v>
@@ -1208,7 +1208,7 @@
         <v>0.1990045279292699</v>
       </c>
       <c r="V3" t="n">
-        <v>0.00074854209431229</v>
+        <v>0.0007443679983575424</v>
       </c>
       <c r="W3" t="n">
         <v>0.002338055686444925</v>
@@ -1232,7 +1232,7 @@
         <v>0.09190106783984116</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.1659453367668779</v>
+        <v>0.1659363065237134</v>
       </c>
       <c r="AE3" t="n">
         <v>0.2590677024979518</v>
@@ -1316,7 +1316,7 @@
         <v>-0.0002415464123152966</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.00659751313903484</v>
+        <v>0.006593256008340927</v>
       </c>
       <c r="BG3" t="n">
         <v>0.02030650766320145</v>
@@ -1364,7 +1364,7 @@
         <v>0.02794660883228155</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0.00171240718540539</v>
+        <v>-0.001712293546975599</v>
       </c>
       <c r="BW3" t="n">
         <v>-0.003544014911570366</v>
@@ -1428,7 +1428,7 @@
         <v>0.04271683546403473</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03926876505534446</v>
+        <v>0.03928910955214671</v>
       </c>
       <c r="F4" t="n">
         <v>0.009550475779563907</v>
@@ -1437,10 +1437,10 @@
         <v>0.07826652761241565</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03017053053196349</v>
+        <v>0.03017227368993634</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0011782179852572</v>
+        <v>0.001196607326473049</v>
       </c>
       <c r="J4" t="n">
         <v>0.01919805789390202</v>
@@ -1455,10 +1455,10 @@
         <v>0.02780490079754477</v>
       </c>
       <c r="N4" t="n">
-        <v>0.07006011560450978</v>
+        <v>0.07005105481107707</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01749753774067651</v>
+        <v>0.01750429248735824</v>
       </c>
       <c r="P4" t="n">
         <v>0.01836187315165091</v>
@@ -1467,7 +1467,7 @@
         <v>0.01356327405758071</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02679270665293706</v>
+        <v>0.02679538191138489</v>
       </c>
       <c r="S4" t="n">
         <v>0.1632381977337289</v>
@@ -1479,7 +1479,7 @@
         <v>0.09207602469592475</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001181047578141217</v>
+        <v>0.001173790713770389</v>
       </c>
       <c r="W4" t="n">
         <v>0.01327814883952942</v>
@@ -1503,7 +1503,7 @@
         <v>0.09015224066563503</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.1108620354048432</v>
+        <v>0.110868550877043</v>
       </c>
       <c r="AE4" t="n">
         <v>0.1332411941003131</v>
@@ -1587,7 +1587,7 @@
         <v>0.001720154638246427</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.02412519315681922</v>
+        <v>0.02412575593895944</v>
       </c>
       <c r="BG4" t="n">
         <v>0.03691776184363592</v>
@@ -1635,7 +1635,7 @@
         <v>0.02913283690927635</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.01164428488806418</v>
+        <v>0.01163225527476877</v>
       </c>
       <c r="BW4" t="n">
         <v>0.009510861775377452</v>
@@ -1774,7 +1774,7 @@
         <v>-0.04541446208112879</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.06732804232804236</v>
+        <v>-0.06737213403880074</v>
       </c>
       <c r="AE5" t="n">
         <v>0.003747795414462041</v>
@@ -1906,7 +1906,7 @@
         <v>-0.03475046210720883</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.02464726631393303</v>
+        <v>-0.02460317460317464</v>
       </c>
       <c r="BW5" t="n">
         <v>-0.02336860670194005</v>
@@ -1979,7 +1979,7 @@
         <v>-0.01343424203109042</v>
       </c>
       <c r="H6" t="n">
-        <v>0.003624708151986664</v>
+        <v>0.003592436207064123</v>
       </c>
       <c r="I6" t="n">
         <v>-0.0002038594688158979</v>
@@ -2021,7 +2021,7 @@
         <v>0.1683903298839883</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.0002032731485790751</v>
+        <v>-0.0002369961701618045</v>
       </c>
       <c r="W6" t="n">
         <v>-2.410865347557683e-05</v>
@@ -2241,7 +2241,7 @@
         <v>0.01378125230247808</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02519363166953529</v>
+        <v>0.02517211703958692</v>
       </c>
       <c r="F7" t="n">
         <v>-0.0008733581746520835</v>
@@ -2400,7 +2400,7 @@
         <v>-0.0004597068418383088</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.003517874347426697</v>
+        <v>0.003496588693957137</v>
       </c>
       <c r="BG7" t="n">
         <v>0.03079574731986446</v>
@@ -2524,7 +2524,7 @@
         <v>0.02641107474844871</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001826192842060434</v>
+        <v>0.001858409336905795</v>
       </c>
       <c r="J8" t="n">
         <v>0.01677192199532373</v>
@@ -2542,7 +2542,7 @@
         <v>0.06464066082269698</v>
       </c>
       <c r="O8" t="n">
-        <v>0.007124173385270399</v>
+        <v>0.007134930700244582</v>
       </c>
       <c r="P8" t="n">
         <v>0.01761888421482271</v>
@@ -2551,7 +2551,7 @@
         <v>0.01163370116211467</v>
       </c>
       <c r="R8" t="n">
-        <v>0.02050224612218837</v>
+        <v>0.02053749048309061</v>
       </c>
       <c r="S8" t="n">
         <v>0.4811712284307892</v>
@@ -2587,7 +2587,7 @@
         <v>0.1209760112285823</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.2357993018620422</v>
+        <v>0.2357646438213769</v>
       </c>
       <c r="AE8" t="n">
         <v>0.3627997940367526</v>
@@ -2783,7 +2783,7 @@
         <v>0.0870609981515712</v>
       </c>
       <c r="E9" t="n">
-        <v>0.06798561151079141</v>
+        <v>0.06803057553956839</v>
       </c>
       <c r="F9" t="n">
         <v>0.01776079136690651</v>
@@ -2795,7 +2795,7 @@
         <v>0.07471264367816093</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002345786272806272</v>
+        <v>0.002432667245873177</v>
       </c>
       <c r="J9" t="n">
         <v>0.02320136228182205</v>
@@ -2810,7 +2810,7 @@
         <v>0.06874999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>0.181872852233677</v>
+        <v>0.1818298969072165</v>
       </c>
       <c r="O9" t="n">
         <v>0.02554278416347383</v>
@@ -2834,7 +2834,7 @@
         <v>0.3158502772643254</v>
       </c>
       <c r="V9" t="n">
-        <v>0.002389226759339724</v>
+        <v>0.002345786272806272</v>
       </c>
       <c r="W9" t="n">
         <v>0.0152920962199313</v>
